--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B2" t="n">
-        <v>79879</v>
+        <v>79260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R2" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R3" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131731750</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739133</v>
       </c>
       <c r="B3" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131731750</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131739133</v>
       </c>
       <c r="B3" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R2" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B3" t="n">
-        <v>79883</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R3" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739133</v>
       </c>
       <c r="B2" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131731750</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B2" t="n">
-        <v>79885</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R2" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R3" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R2" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B3" t="n">
-        <v>79885</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R3" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R2" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B3" t="n">
-        <v>79885</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R3" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131739133</v>
       </c>
       <c r="B2" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131731750</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B2" t="n">
-        <v>79893</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R2" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R3" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131731750</v>
+        <v>131739133</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470769</v>
+        <v>471117</v>
       </c>
       <c r="R2" t="n">
-        <v>6864154</v>
+        <v>6864032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131739133</v>
+        <v>131731750</v>
       </c>
       <c r="B3" t="n">
-        <v>79893</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471117</v>
+        <v>470769</v>
       </c>
       <c r="R3" t="n">
-        <v>6864032</v>
+        <v>6864154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>131731750</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -779,7 +779,7 @@
         <v>131739133</v>
       </c>
       <c r="B3" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,6 +870,332 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131738301</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Risåsflon Öst, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>470740</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6864152</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På sälg med stuplav i ungskog som är ca 15 år</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131740512</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risåsflon Öst, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>470737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6864151</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg i ungskog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131739983</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risåsflon Öst, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>470756</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6864148</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosök på flera äldre granar i hänsyn mot myr</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Christer Lindberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 54364-2024 artfynd.xlsx
+++ b/artfynd/A 54364-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739133</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738301</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,8 +1225,20 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739983</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>